--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129742788</v>
+        <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>78833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601295</v>
+        <v>601273</v>
       </c>
       <c r="R3" t="n">
-        <v>6959688</v>
+        <v>6959833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129742454</v>
+        <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>78832</v>
+        <v>91572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601273</v>
+        <v>601279</v>
       </c>
       <c r="R4" t="n">
-        <v>6959833</v>
+        <v>6959688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129742598</v>
+        <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>80054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601295</v>
+        <v>601280</v>
       </c>
       <c r="R5" t="n">
-        <v>6959736</v>
+        <v>6959783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,42 +1063,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129742766</v>
+        <v>129742788</v>
       </c>
       <c r="B6" t="n">
-        <v>91571</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601279</v>
+        <v>601295</v>
       </c>
       <c r="R6" t="n">
         <v>6959688</v>
@@ -1154,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,45 +1170,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129742520</v>
+        <v>129742598</v>
       </c>
       <c r="B7" t="n">
-        <v>80053</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>392</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601280</v>
+        <v>601295</v>
       </c>
       <c r="R7" t="n">
-        <v>6959783</v>
+        <v>6959736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91572</v>
+        <v>91577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>80054</v>
+        <v>80059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91577</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>80059</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129742788</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129742598</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
+        <v>91589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>80062</v>
+        <v>80065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129742788</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129742598</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91589</v>
+        <v>91590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>80065</v>
+        <v>80066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129742486</v>
       </c>
       <c r="B2" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129742454</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129742766</v>
       </c>
       <c r="B4" t="n">
-        <v>91590</v>
+        <v>91607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129742520</v>
       </c>
       <c r="B5" t="n">
-        <v>80066</v>
+        <v>80067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80310</v>
+        <v>80311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80223</v>
+        <v>80224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80223</v>
+        <v>80224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80311</v>
+        <v>80313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80224</v>
+        <v>80226</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80224</v>
+        <v>80226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80314</v>
+        <v>80315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80315</v>
+        <v>80318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80228</v>
+        <v>80231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>131106652</v>
       </c>
       <c r="B8" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>131106657</v>
       </c>
       <c r="B9" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131106656</v>
       </c>
       <c r="B10" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>131106658</v>
       </c>
       <c r="B12" t="n">
-        <v>80231</v>
+        <v>80232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129742486</v>
+        <v>129742520</v>
       </c>
       <c r="B2" t="n">
-        <v>80103</v>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601273</v>
+        <v>601280</v>
       </c>
       <c r="R2" t="n">
-        <v>6959833</v>
+        <v>6959783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129742454</v>
+        <v>131106656</v>
       </c>
       <c r="B3" t="n">
-        <v>78851</v>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601273</v>
+        <v>601270</v>
       </c>
       <c r="R3" t="n">
-        <v>6959833</v>
+        <v>6959748</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,14 +844,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2025_0520</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,57 +886,70 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129742766</v>
+        <v>131106658</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601279</v>
+        <v>601282</v>
       </c>
       <c r="R4" t="n">
-        <v>6959688</v>
+        <v>6959785</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -932,14 +974,29 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2025_0518</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,44 +1011,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Samuel Koont</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129742520</v>
+        <v>129742766</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601280</v>
+        <v>601279</v>
       </c>
       <c r="R5" t="n">
-        <v>6959783</v>
+        <v>6959688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129742788</v>
+        <v>112538846</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,39 +1135,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601295</v>
+        <v>601223</v>
       </c>
       <c r="R6" t="n">
-        <v>6959688</v>
+        <v>6959727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1133,17 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1158,22 +1209,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129742598</v>
+        <v>129742454</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,39 +1232,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601295</v>
+        <v>601273</v>
       </c>
       <c r="R7" t="n">
-        <v>6959736</v>
+        <v>6959833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1292,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,45 +1318,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131106652</v>
+        <v>131106660</v>
       </c>
       <c r="B8" t="n">
-        <v>80319</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601273</v>
+        <v>601244</v>
       </c>
       <c r="R8" t="n">
-        <v>6959781</v>
+        <v>6959831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,7 +1392,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025_0524</t>
+          <t>2025_0516</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1352,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1362,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>aspstubbe</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,7 +1432,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Samuel Koont</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1398,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131106657</v>
+        <v>131106661</v>
       </c>
       <c r="B9" t="n">
-        <v>80359</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,31 +1454,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1442,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601264</v>
+        <v>601240</v>
       </c>
       <c r="R9" t="n">
-        <v>6959676</v>
+        <v>6959782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1517,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025_0519</t>
+          <t>2025_0515</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1482,7 +1527,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1492,12 +1537,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>gammal asp</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,54 +1573,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131106656</v>
+        <v>129742486</v>
       </c>
       <c r="B10" t="n">
-        <v>80232</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lappberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601270</v>
+        <v>601273</v>
       </c>
       <c r="R10" t="n">
-        <v>6959748</v>
+        <v>6959833</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,34 +1636,14 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2025_0520</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>08:43</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>08:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>asphögstubbe</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,26 +1658,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kustpaketet</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>131106655</v>
       </c>
       <c r="B11" t="n">
-        <v>80359</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,32 +1795,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131106658</v>
+        <v>131106657</v>
       </c>
       <c r="B12" t="n">
-        <v>80232</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1827,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601282</v>
+        <v>601264</v>
       </c>
       <c r="R12" t="n">
-        <v>6959785</v>
+        <v>6959676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,7 +1869,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025_0518</t>
+          <t>2025_0519</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1867,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1889,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>gammal asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,7 +1914,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1911,11 +1928,11 @@
         <v>131106662</v>
       </c>
       <c r="B13" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2026,6 +2043,341 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129742598</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601295</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6959736</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129742788</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601295</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6959688</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131106652</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lappberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601273</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6959781</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2025_0524</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>aspstubbe</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 46079-2025 artfynd.xlsx
+++ b/artfynd/A 46079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742520</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538846</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106660</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106661</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742486</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106655</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106662</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742598</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2261,6 +2331,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742788</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2382,8 +2457,30 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106652</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>